--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_weapon/lang_weapon__name_title__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_weapon/lang_weapon__name_title__part_0001.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Primordial Broadblade</t>
+          <t>Primordial Đại kiếm</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Primordial Rectifier</t>
+          <t>Primordial Pháp khí</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Broadblade prototype: REGULARIZATION</t>
+          <t>Đại kiếm prototype: REGULARIZATION</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Rectifier prototype: SEQUENCE</t>
+          <t>Pháp khí prototype: SEQUENCE</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Broadblade improved: regularization II</t>
+          <t>Đại kiếm improved: regularization II</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Rectifier improved: SEQUENCE II</t>
+          <t>Pháp khí improved: SEQUENCE II</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
